--- a/samples/ss_prbc_ingest.xlsx
+++ b/samples/ss_prbc_ingest.xlsx
@@ -774,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U80"/>
+  <dimension ref="A1:U91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="14" min="1" max="1"/>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E23" s="20" t="n">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E24" s="20" t="n">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E35" s="20" t="n">
@@ -3652,6 +3652,599 @@
     <row r="78"/>
     <row r="79"/>
     <row r="80"/>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>44</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>GITET BKASI</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>GITET_BKASI</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Busbar GITET</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>500 kV</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Boundary_External: 500/150 kV source</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>45</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>IBT 2 BKASI</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>IBT 2 BKASI</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>GITET_BKASI</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>BKASI</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>46</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>IBT 4 BKASI</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>IBT 4 BKASI</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>GITET_BKASI</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>BKASI</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>47</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>GITET MTWAR</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>GITET_MTWAR</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Busbar GITET</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>500 kV</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Boundary_External: 500/150 kV source</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>48</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>IBT 1 MTWAR</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>IBT 1 MTWAR</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>GITET_MTWAR</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>MTWAR</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>49</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>IBT 2 MTWAR</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>IBT 2 MTWAR</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>GITET_MTWAR</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>MTWAR</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>50</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>GITET CWBRU</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>GITET_CWBRU</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Busbar GITET</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>500 kV</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Boundary_External: 500/150 kV source</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>51</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>IBT 1 CWBRU</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>IBT 1 CWBRU</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>GITET_CWBRU</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>CWBRU</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>52</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PLTGU Muarakarang ST 3.0</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>KIT_MKR_ST30</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Pembangkit</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Boundary_External: Source / generator</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>53</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PLTGU Priok Blok 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>KIT_PRIOK_B12</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Pembangkit</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Boundary_External: Source / generator</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>54</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PLTGU Priok Blok 3</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>KIT_PRIOK_B3</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Pembangkit</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Boundary_External: Source / generator</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3663,7 +4256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q100"/>
+  <dimension ref="A1:Q103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="14" min="1" max="1"/>
@@ -7033,6 +7626,168 @@
     <row r="98"/>
     <row r="99"/>
     <row r="100"/>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>52</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Outlet PLTGU Muarakarang ST 3.0</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>KIT_MKR_ST30</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>MKLMA</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>1</v>
+      </c>
+      <c r="O101" t="n">
+        <v>1</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>53</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Outlet PLTGU Priok Blok 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>KIT_PRIOK_B12</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>PRBRT</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>1</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1</v>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>54</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Outlet PLTGU Priok Blok 3</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>KIT_PRIOK_B3</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>PRTRU</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Jakarta &amp; Banten</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>1</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7044,7 +7799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="14" min="1" max="1"/>
@@ -7247,6 +8002,135 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40"/>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PDKLP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PDKLP (boundary stub di BKASI)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BKASI</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Boundary / external</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Belum Operasi</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Boundary_External; source evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SKTNI</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SKTNI (boundary stub di BKASI)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BKASI</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Boundary / external</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Belum Operasi</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Boundary_External; source evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SMRCN</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SMRCN (boundary stub di BKASI)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BKASI</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Boundary / external</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Belum Operasi</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Boundary_External; source evidence</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/samples/ss_prbc_ingest.xlsx
+++ b/samples/ss_prbc_ingest.xlsx
@@ -913,7 +913,7 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>Muara Karang / MKLMA</t>
+          <t>Muarakarang Lama</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>Priok Timur</t>
+          <t>Priok Timur Baru</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>Priok Baru / Unit 3 side</t>
+          <t>Priok Timur Lama</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>PLNDO</t>
+          <t>Pulo Mas Indo (KTT)</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>PGSAN</t>
+          <t>Pegangsaan</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>PLPRU</t>
+          <t>Pulo Gadung Baru</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>PLPNG20</t>
+          <t>Plumpang (20 KA)</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>PLPNG40</t>
+          <t>Plumpang (40 KA)</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>KLBRU</t>
+          <t>Kelapa Baru (KTT)</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>GMBRU</t>
+          <t>Gambir Baru</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>SNTER</t>
+          <t>Sunter</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>GNSHR</t>
+          <t>Gunung Sahari</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>PDMGN</t>
+          <t>Pademangan</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>MGBSR</t>
+          <t>Menteng Besar</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>PKRNG</t>
+          <t>Pekayon Raya</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>KLPGD</t>
+          <t>Kelapa Gading</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>GDPLA</t>
+          <t>GIS Gedung Pola</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>Bekasi 150 kV</t>
+          <t>Bekasi (bus 150 kV)</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>Muaratawar 150 kV</t>
+          <t>Muaratawar (bus 150 kV)</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>PGDRU</t>
+          <t>Pegangsaan Dua</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>PGLNG</t>
+          <t>Penggilingan</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>RATER</t>
+          <t>Rawa Terate</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>MRNDA</t>
+          <t>Marunda</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>HNDAH</t>
+          <t>Harapan Indah</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>KDSPI</t>
+          <t>Kandang Sapi</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>PGDNGK</t>
+          <t>Pegangsaan Konv</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>RAKUN</t>
+          <t>Rawa Kucing</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>RAWAM</t>
+          <t>Rawa Makmur</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>Cawang Baru 150 kV</t>
+          <t>Cawang Baru (bus 150 kV)</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>CNANG</t>
+          <t>Cinang / Cawang Baru bawah</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>PLMAS</t>
+          <t>Pulo Mas</t>
         </is>
       </c>
       <c r="C37" s="16" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>CMPTH</t>
+          <t>Cempaka Putih</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>MGRAI</t>
+          <t>GIS Manggarai</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>TMTGI</t>
+          <t>Tomang Tinggi</t>
         </is>
       </c>
       <c r="C40" s="16" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>GMLMA</t>
+          <t>Gambir Lama</t>
         </is>
       </c>
       <c r="C41" s="16" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>DKTAS</t>
+          <t>GIS Dukuh Atas</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>KBSRH</t>
+          <t>GIS Kebon Sirih</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>STBDI</t>
+          <t>Setiabudi</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GITET BKASI</t>
+          <t>GITET Bekasi</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IBT 2 BKASI</t>
+          <t>IBT 2 Bekasi</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GITET MTWAR</t>
+          <t>GITET Muaratawar</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IBT 1 MTWAR</t>
+          <t>IBT 1 Muaratawar</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GITET CWBRU</t>
+          <t>GITET Cawang Baru</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IBT 1 CWBRU</t>
+          <t>IBT 1 Cawang Baru</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">

--- a/samples/ss_prbc_ingest.xlsx
+++ b/samples/ss_prbc_ingest.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="14" min="1" max="1"/>
@@ -541,6 +541,18 @@
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Multi Pin</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1018,8 +1030,16 @@
           <t>Root / source side</t>
         </is>
       </c>
-      <c r="P3" s="16" t="n"/>
-      <c r="Q3" s="16" t="n"/>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q3" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R3" s="16" t="inlineStr">
         <is>
           <t>Jakarta &amp; Banten</t>
@@ -1081,8 +1101,16 @@
           <t>Root / source side</t>
         </is>
       </c>
-      <c r="P4" s="16" t="n"/>
-      <c r="Q4" s="16" t="n"/>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R4" s="16" t="inlineStr">
         <is>
           <t>Jakarta &amp; Banten</t>
@@ -1144,8 +1172,16 @@
           <t>Root / generation side</t>
         </is>
       </c>
-      <c r="P5" s="16" t="n"/>
-      <c r="Q5" s="16" t="n"/>
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q5" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R5" s="16" t="inlineStr">
         <is>
           <t>Jakarta &amp; Banten</t>
@@ -1459,8 +1495,16 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="P10" s="16" t="n"/>
-      <c r="Q10" s="16" t="n"/>
+      <c r="P10" s="16" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q10" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R10" s="16" t="inlineStr">
         <is>
           <t>Jakarta &amp; Banten</t>
@@ -1585,8 +1629,16 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="16" t="n"/>
+      <c r="P12" s="16" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q12" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R12" s="16" t="inlineStr">
         <is>
           <t>Jakarta &amp; Banten</t>
@@ -1648,8 +1700,16 @@
           <t>Stitch anchor</t>
         </is>
       </c>
-      <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="16" t="n"/>
+      <c r="P13" s="16" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q13" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R13" s="16" t="inlineStr">
         <is>
           <t>Jakarta &amp; Banten</t>
@@ -2215,8 +2275,16 @@
           <t>Stitch anchor</t>
         </is>
       </c>
-      <c r="P22" s="16" t="n"/>
-      <c r="Q22" s="16" t="n"/>
+      <c r="P22" s="16" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q22" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R22" s="16" t="inlineStr">
         <is>
           <t>Jakarta &amp; Banten</t>
@@ -4191,6 +4259,16 @@
           <t>SOURCE</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R90" t="inlineStr">
         <is>
           <t>Jakarta &amp; Banten</t>
@@ -4237,6 +4315,16 @@
       <c r="O91" t="inlineStr">
         <is>
           <t>SOURCE</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -5062,7 +5150,11 @@
       <c r="A13" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="16" t="n"/>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
           <t>SUTT PRBRT - PLPNG40</t>
@@ -5094,7 +5186,7 @@
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="K13" s="20" t="n"/>
@@ -5125,7 +5217,11 @@
       <c r="A14" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="16" t="n"/>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
           <t>SUTT PRTMR - PRTRU</t>
@@ -5157,7 +5253,7 @@
       </c>
       <c r="J14" s="20" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="K14" s="20" t="n"/>
@@ -5188,7 +5284,11 @@
       <c r="A15" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="16" t="n"/>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
           <t>SUTT PRTMR - PLPNG20</t>
@@ -5220,7 +5320,7 @@
       </c>
       <c r="J15" s="20" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="K15" s="20" t="n"/>
@@ -5944,7 +6044,11 @@
       <c r="A27" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="16" t="n"/>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
           <t>SUTT GDPLA - MGRAI</t>
@@ -5976,7 +6080,7 @@
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="K27" s="20" t="n"/>
@@ -6574,7 +6678,11 @@
       <c r="A37" s="20" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="16" t="n"/>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C37" s="16" t="inlineStr">
         <is>
           <t>SUTT PGLNG - RATER</t>
@@ -6606,7 +6714,7 @@
       </c>
       <c r="J37" s="20" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="K37" s="20" t="n"/>
@@ -7330,7 +7438,11 @@
       <c r="A49" s="20" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="16" t="n"/>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C49" s="16" t="inlineStr">
         <is>
           <t>SUTT MGRAI - DKTAS</t>
@@ -7362,7 +7474,7 @@
       </c>
       <c r="J49" s="20" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="K49" s="20" t="n"/>
@@ -8142,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="14" min="1" max="1"/>
@@ -8191,35 +8303,251 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>JBB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N-1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[N-1] Tidak ada PMT pada interconnector-1&amp;2 Priok Timur Lama arah Priok Barat.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1. Pemeliharaan Interconnector pada ruas tersebut sulit dilakukan karena harus memadamkan busbar GIS Priok Barat. 2. Apabila terjadi gangguan pada interconnector berdampak padam busbar pada GIS 150 kV Priok Barat dan GIS 150 kV Priok Timur.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pengaturan penjadwalan pemeliharaan dilakukan bersamaan pekerjaan pemeliharaan busbar.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Jangka Pendek: Usulan penambahan PMT bay Interconnector-1&amp;2 Priok Barat GIS Priok Timur Lama. Rencana COD Tahun 2028.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>JBB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N-2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[N-2] Terdapat permasalahan tower combine pada ruas SUTT Priok Barat - Plumpang Baru dan Priok Timur Baru - Plumpang.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1. Pemeliharaan pada ruas tersebut sulit dilakukan. 2. Evolusi subsistem sulit dilakukan.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1. Pengaturan pembangkitan saat pemeliharaan. 2. Penjadwalan pemeliharaan disamakan dengan jadwal pemeliharaan pembangkitan.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Jangka Menengah: Usulan pembangunan SKTT Priok Timur Baru-Sunter-Kandang Sapi dan SKTT Kemayoran-Cempaka Putih. Rencana COD Tahun 2030.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JBB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[N-1] Konfigurasi SKTT 150 kV Manggarai-Gedung Pola dan SKTT 150 kV Manggarai-Dukuh Atas hanya ada 1 sirkit (Pelanggan VVIP masuk kategori zero down time). Jika hanya ada 1 sirkit maka konfigurasi tersebut menjadi kurang andal.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Terjadi pemadaman di GIS Gedung Pola dan GIS Dukuh Atas sebesar 89 MW (Data EOB 2024) apabila gangguan pada SKTT 150 kV Manggarai-Dukuh Atas.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pengaturan beban (Splitting Busbar di GIS Gedung Pola dan Dukuh Atas).</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Jangka Pendek: 1. Pembangunan sirkit ke-2 SKTT 150 kV Manggarai-Dukuh Atas (RUPTL 2025-2034, COD 2026). 2. Pembangunan sirkit ke-2 SKTT 150 kV Manggarai-Gedung Pola (RUPTL 2025-2034, COD 2027).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JBB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>N-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[N-1] Terjadi kerusakan/Breakdown pada Bay Line-1 penghantar SUTT 150 kV Penggilingan-Rawa Terate (Ex-Bay Pulogadung Baru) sehingga konfigurasi yang tadinya Double Phi menjadi tidak andal karena masih Single Phi (di GIS Penggilingan).</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pada saat pemeliharaan harus mempertimbangkan kemampuan kapasitas penghantar.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Jangka Pendek: Percepatan perbaikan Line Bay-1 Arah Rater dan Line Bay-1 Bekasi, Material sudah onsite Oktober 2023 (sudah terkontrak). Perkiraan COD tahun 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JBB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>N-1-1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[N-1-1] Terjadi fenomena power swing saat gangguan di SS Priok-Cawang 1-Bekasi 2,4 yang menyebabkan Pembangkitan Priok ikut trip.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Subsistem mengalami pemadaman meluas dan menyebabkan keandalan berkurang.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1. Sudah dilakukan penugasan studi ke Akademisi LAPI ITB untuk menganalisa fenomena power swing di SS Priok (2021). 2. Pemasangan Defense Scheme OLS IBT untuk Splitting IBT Cawang dan IBT Bekasi jika terjadi gangguan N-2-1.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Jangka Pendek: 1. Pembangunan SUTET 500 kV Muaratawar-Priok untuk Re-konfigurasi subsistem (RUPTL 2025-2034, COD timeline proyek Des 2026). 2. Pembangunan outlet IBT GITET Muaratawar SUTT Muaratawar-Inc Bekasi-Plumpang/Kandang Sapi (Nov 2026). 3. Usulan Section pada GIS 150 kV Pegangsaan (COD 2027).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JBB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>N-1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[N-1] Terjadi fenomena arus 3 I0 pada subsistem Priok-Cawang-Bekasi di sekitar GI Priok Barat - Priok Timur - Priok Timur Baru - Plumpang - Pegangsaan dan sekitarnya.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Terjadinya trip penghantar akibat relay GFR bekerja, padahal tidak ada gangguan eksternal.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1. Penugasan studi dari UIT JBB ke Puslitbang untuk menganalisa fenomena 3 I0 (2021). 2. UIT JBB menaikkan setting GFR. 3. Pengaturan pola operasi pembangkit saat ada pekerjaan di ruas Priok Barat-Priok Timur-Priok Timur Baru.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Jangka Pendek: Pembangunan SUTET 500 kV Muaratawar-Priok untuk Re-konfigurasi subsistem (RUPTL 2025-2034, COD timeline proyek Des 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JBB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>N-1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[N-1] GIS Gedung Pola merupakan pasokan VVIP ke beberapa kantor duta besar negara-negara (Zero downtime) sehingga keandalan GIS tersebut menjadi prioritas namun GIS Gedungpola masih beroperasi dengan single busbar sehingga ketika terjadi gangguan busbar pada GIS Gedungpola akan berdampak padam GIS.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1. Keandalan berkurang untuk pasokan VVIP (zero downtime) di GIS Gedung Pola karena masih single busbar. 2. Kesulitan dalam pemeliharaan busbar.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Manuver beban trafo di GIS Gedung Pola melalui 20 kV.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Jangka Pendek: Pemasangan double busbar GIS Gedung Pola (satu lingkup pekerjaan sirkit ke-2 SKTT 150 kV Manggarai-Gedung Pola, rencana COD Tahun 2027).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
